--- a/downloads/loesungen/09_Zoo_3NF_Loesung.xlsx
+++ b/downloads/loesungen/09_Zoo_3NF_Loesung.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEHEGE_TIER" sheetId="1" r:id="R597ce77b00514065"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PFLEGER" sheetId="2" r:id="Re45cedb48f3c4dba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEHEGE" sheetId="3" r:id="R74f18c23dfe4482e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BEREICH" sheetId="4" r:id="R012b36df53e1435e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEHEGE_TIER" sheetId="1" r:id="R3c41496ffda74c14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PFLEGER" sheetId="2" r:id="R217e7a4271a64689"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEHEGE" sheetId="3" r:id="R4c6bc0abcd93415d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BEREICH" sheetId="4" r:id="R73a7a0a7ad344766"/>
   </x:sheets>
 </x:workbook>
 </file>
